--- a/stories/arbres/ATOM-TMP.SEM.001-05.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Thibault est dans le salon. Maman ouvre un calendrier. Maman dit : il y a sept jours dans l'ordre. Lundi. Mardi. Mercredi. Jeudi. Vendredi. Samedi. Dimanche. Thibault pose le doigt. Il répète un jour : jeudi. Maman recommence. Thibault dit : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Sept jours dans l'ordre.</t>
+          <t>Thibault est dans le salon. Maman ouvre un calendrier. Il y a sept jours dans l'ordre. Lundi. Mardi. Mercredi. Jeudi. Vendredi. Samedi. Dimanche. Thibault pose le doigt. Il répète un jour : jeudi. Maman recommence. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Sept jours dans l'ordre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Thibault est dans le salon. Maman ouvre un calendrier.
+maman|Il y a sept jours dans l'ordre. Lundi. Mardi. Mercredi. Jeudi. Vendredi. Samedi. Dimanche.
+narrateur|Thibault pose le doigt. Il répète un jour : jeudi. Maman recommence.
+enfant-m|Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Sept jours dans l'ordre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Thibault touche le calendrier. Que dit-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Thibault a dit les sept jours dans l'ordre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1825,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range le calendrier. Thibault sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1992,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2032,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.001-05.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 enfant-m|Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Sept jours dans l'ordre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Thibault touche le calendrier. Que dit-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Thibault a dit les sept jours dans l'ordre.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1830,6 +1838,7 @@
           <t>narrateur|Maman range le calendrier. Thibault sourit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1997,6 +2006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2015,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2039,6 +2049,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2240,6 +2264,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.SEM.001-05.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thibault dit les sept jours</t>
+          <t>Le poisson et le gâteau</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël veut le gâteau de samedi. Vendredi, ils vont au port pour le poisson. L'étal range la glace. Samedi, un œuf roule. Il le rattrape. Le gâteau dore.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Thibault est dans le salon. Maman ouvre un calendrier. Il y a sept jours dans l'ordre. Lundi. Mardi. Mercredi. Jeudi. Vendredi. Samedi. Dimanche. Thibault pose le doigt. Il répète un jour : jeudi. Maman recommence. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Sept jours dans l'ordre.</t>
+          <t>Une écaille d'argent brille entre deux planches. Les cordes des bateaux claquent contre le bois. L'air sent le sel et le citron. Une caisse de glace fume tout bas. Tu as vu l'écaille, Raphaël ? Elle brille. C'est vendredi. Vendredi, on prend le poisson du port. En ce moment, Raphaël touche la glace. Elle pique ses doigts. Je veux le gâteau. Le gâteau de demain. Demain, c'est samedi. Samedi, on le fait. D'abord le poisson. L'étal range déjà les caisses. Un tas de glace glisse vers le bord. Ils s'en vont. On demande le petit. Maman montre un poisson court. Il a l'œil encore clair. Celui-là. Le papier se ferme, tout froid. Vendredi, le port. Samedi, la farine. La semaine a sept jours. Quel jour vient après vendredi ? Samedi. Oui. Raphaël tient le sac contre lui. Le poisson tape, tout mou. Il sent la mer. On rentre. Une mouette crie au-dessus du quai. L'écaille reste coincée entre les planches.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Thibault est dans le salon. Maman ouvre un calendrier. Maman dit : il y a &lt;emphasis level="moderate"&gt;sept&lt;/emphasis&gt; jours dans l'ordre. Lundi. Mardi. Mercredi. Jeudi. Vendredi. Samedi. Dimanche. Thibault pose le doigt. Il répète un jour : jeudi. Maman recommence. Thibault dit : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Sept jours dans l'ordre.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une écaille d'argent brille entre deux planches. Les cordes des bateaux claquent contre le bois. L'air sent le sel et le citron. Une caisse de glace fume tout bas. Tu as vu l'écaille, Raphaël ? Elle brille. C'est vendredi. Vendredi, on prend le poisson du port. En ce moment, Raphaël touche la glace. Elle pique ses doigts. Je veux le gâteau. Le gâteau de demain. Demain, c'est samedi. Samedi, on le fait. D'abord le poisson. L'étal range déjà les caisses. Un tas de glace glisse vers le bord. Ils s'en vont. On demande le petit. Maman montre un poisson court. Il a l'œil encore clair. Celui-là. Le papier se ferme, tout froid. Vendredi, le port. Samedi, la farine. La semaine a sept jours. Quel jour vient après vendredi ? Samedi. Oui. Raphaël tient le sac contre lui. Le poisson tape, tout mou. Il sent la mer. On rentre. Une mouette crie au-dessus du quai. L'écaille reste coincée entre les planches.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,43 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Thibault est dans le salon. Maman ouvre un calendrier.
-maman|Il y a sept jours dans l'ordre. Lundi. Mardi. Mercredi. Jeudi. Vendredi. Samedi. Dimanche.
-narrateur|Thibault pose le doigt. Il répète un jour : jeudi. Maman recommence.
-enfant-m|Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Sept jours dans l'ordre.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une écaille d'argent brille entre deux planches.
+narrateur|Les cordes des bateaux claquent contre le bois.
+narrateur|L'air sent le sel et le citron.
+narrateur|Une caisse de glace fume tout bas.
+maman|Tu as vu l'écaille, Raphaël ?
+enfant-m|Elle brille.
+maman|C'est vendredi.
+maman|Vendredi, on prend le poisson du port.
+narrateur|En ce moment, Raphaël touche la glace.
+narrateur|Elle pique ses doigts.
+enfant-m|Je veux le gâteau.
+enfant-m|Le gâteau de demain.
+maman|Demain, c'est samedi.
+maman|Samedi, on le fait.
+maman|D'abord le poisson.
+narrateur|L'étal range déjà les caisses.
+narrateur|Un tas de glace glisse vers le bord.
+enfant-m|Ils s'en vont.
+maman|On demande le petit.
+narrateur|Maman montre un poisson court.
+narrateur|Il a l'œil encore clair.
+enfant-m|Celui-là.
+narrateur|Le papier se ferme, tout froid.
+maman|Vendredi, le port.
+maman|Samedi, la farine.
+maman|La semaine a sept jours.
+maman|Quel jour vient après vendredi ?
+enfant-m|Samedi.
+maman|Oui.
+narrateur|Raphaël tient le sac contre lui.
+narrateur|Le poisson tape, tout mou.
+enfant-m|Il sent la mer.
+maman|On rentre.
+narrateur|Une mouette crie au-dessus du quai.
+narrateur|L'écaille reste coincée entre les planches.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,12 +1385,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Thibault touche le calendrier. Que dit-il ?</t>
+          <t>Après vendredi, quel jour vient ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Thibault touche le calendrier. Que dit-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Après vendredi, quel jour vient ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1358,12 +1400,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>lundi</t>
+          <t>samedi</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>lundi | jeudi | sept jours | un jour</t>
+          <t>samedi | le samedi | c'est samedi</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1378,7 +1420,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il y a sept jours. Dans quel ordre ?</t>
+          <t>Vendredi, le port. Quel jour vient après ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1427,7 +1469,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1499,10 +1541,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Thibault touche le calendrier. Que dit-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Après vendredi, quel jour vient ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1527,12 +1568,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Thibault a dit les sept jours dans l'ordre.</t>
+          <t>Le lendemain, la cuisine sent le citron. Un sac de farine attend sur la table. C'est samedi, Raphaël. Le jour du gâteau. Je casse l'œuf ? Tout doux. L'œuf roule vers le bord. Raphaël tend la main. Il le rattrape contre la farine. Je l'ai. Merci, Raphaël. Tu as rattrapé l'œuf. Ils cassent l'œuf dans le bol. La farine fait un nuage blanc. Il neige. Un peu. La pâte devient jaune, puis lisse. Au four. La porte du four claque, tiède.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Thibault a dit les &lt;emphasis level="moderate"&gt;sept&lt;/emphasis&gt; jours dans l'ordre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le lendemain, la cuisine sent le citron. Un sac de farine attend sur la table. C'est samedi, Raphaël. Le jour du gâteau. Je casse l'œuf ? Tout doux. L'œuf roule vers le bord. Raphaël tend la main. Il le rattrape contre la farine. Je l'ai. Merci, Raphaël. Tu as rattrapé l'œuf. Ils cassent l'œuf dans le bol. La farine fait un nuage blanc. Il neige. Un peu. La pâte devient jaune, puis lisse. Au four. La porte du four claque, tiède.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1595,7 +1636,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1671,10 +1712,27 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Thibault a dit les sept jours dans l'ordre.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le lendemain, la cuisine sent le citron.
+narrateur|Un sac de farine attend sur la table.
+maman|C'est samedi, Raphaël.
+maman|Le jour du gâteau.
+enfant-m|Je casse l'œuf ?
+maman|Tout doux.
+narrateur|L'œuf roule vers le bord.
+narrateur|Raphaël tend la main.
+narrateur|Il le rattrape contre la farine.
+enfant-m|Je l'ai.
+maman|Merci, Raphaël.
+maman|Tu as rattrapé l'œuf.
+narrateur|Ils cassent l'œuf dans le bol.
+narrateur|La farine fait un nuage blanc.
+enfant-m|Il neige.
+maman|Un peu.
+narrateur|La pâte devient jaune, puis lisse.
+maman|Au four.
+narrateur|La porte du four claque, tiède.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1699,12 +1757,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range le calendrier. Thibault sourit.</t>
+          <t>Le gâteau dore derrière la vitre. La cuisine sent le beurre chaud. Vendredi, le poisson. Samedi, le gâteau. Les deux jours. Oui. Raphaël colle le nez à la vitre. Le gâteau gonfle, tout lent. Il est presque prêt. Encore un peu. Le sac du poisson, lui, est déjà vide. Il reste une odeur de sel sur le manteau. On le sort ? Oui. Le gâteau tremble, puis se tient. Il est à nous. Oui. Tu as attendu samedi. Une miette de citron brille sur la table. Raphaël pose la spatule, encore farineuse.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range le calendrier. Thibault sourit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le gâteau dore derrière la vitre. La cuisine sent le beurre chaud. Vendredi, le poisson. Samedi, le gâteau. Les deux jours. Oui. Raphaël colle le nez à la vitre. Le gâteau gonfle, tout lent. Il est presque prêt. Encore un peu. Le sac du poisson, lui, est déjà vide. Il reste une odeur de sel sur le manteau. On le sort ? Oui. Le gâteau tremble, puis se tient. Il est à nous. Oui. Tu as attendu samedi. Une miette de citron brille sur la table. Raphaël pose la spatule, encore farineuse.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1767,7 +1825,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1835,10 +1893,28 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range le calendrier. Thibault sourit.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le gâteau dore derrière la vitre.
+narrateur|La cuisine sent le beurre chaud.
+maman|Vendredi, le poisson.
+maman|Samedi, le gâteau.
+enfant-m|Les deux jours.
+maman|Oui.
+narrateur|Raphaël colle le nez à la vitre.
+narrateur|Le gâteau gonfle, tout lent.
+enfant-m|Il est presque prêt.
+maman|Encore un peu.
+narrateur|Le sac du poisson, lui, est déjà vide.
+narrateur|Il reste une odeur de sel sur le manteau.
+maman|On le sort ?
+enfant-m|Oui.
+narrateur|Le gâteau tremble, puis se tient.
+enfant-m|Il est à nous.
+maman|Oui.
+maman|Tu as attendu samedi.
+narrateur|Une miette de citron brille sur la table.
+narrateur|Raphaël pose la spatule, encore farineuse.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1863,12 +1939,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël souffle sur le gâteau, tout doux. Il est chaud. Oui. Le port hier, le four maintenant. Une écaille d'argent sèche encore sur la planche du quai.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël souffle sur le gâteau, tout doux. Il est chaud. Oui. Le port hier, le four maintenant. Une écaille d'argent sèche encore sur la planche du quai.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1924,14 +2000,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2003,10 +2079,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Raphaël souffle sur le gâteau, tout doux.
+enfant-m|Il est chaud.
+maman|Oui.
+maman|Le port hier, le four maintenant.
+narrateur|Une écaille d'argent sèche encore sur la planche du quai.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2063,6 +2142,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.001-05.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>port le vendredi, cuisine le samedi</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Thibault, maman</t>
+          <t>Raphaël, maman</t>
         </is>
       </c>
     </row>
